--- a/5/search/FY3_Missile1_results/solutions_direction_153.0.xlsx
+++ b/5/search/FY3_Missile1_results/solutions_direction_153.0.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,7 +517,7 @@
         <v>700</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8999999999999986</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>655.9</v>
       </c>
       <c r="K3" t="n">
-        <v>2.100000000000001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -587,7 +587,7 @@
         <v>680.4</v>
       </c>
       <c r="K4" t="n">
-        <v>2.100000000000001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -622,7 +622,7 @@
         <v>700</v>
       </c>
       <c r="K5" t="n">
-        <v>1.699999999999996</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -657,7 +657,7 @@
         <v>695.1</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -692,7 +692,7 @@
         <v>700</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8999999999999986</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
         <v>621.6</v>
       </c>
       <c r="K8" t="n">
-        <v>1.199999999999996</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -762,7 +762,7 @@
         <v>621.6</v>
       </c>
       <c r="K9" t="n">
-        <v>2.100000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -797,7 +797,7 @@
         <v>621.6</v>
       </c>
       <c r="K10" t="n">
-        <v>1.600000000000001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -832,7 +832,7 @@
         <v>655.9</v>
       </c>
       <c r="K11" t="n">
-        <v>2.100000000000001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -872,37 +872,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="B13" t="n">
-        <v>131.6</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>6000</v>
+        <v>5158.979348109144</v>
       </c>
       <c r="F13" t="n">
-        <v>-368</v>
+        <v>-411.6045852511102</v>
       </c>
       <c r="G13" t="n">
         <v>700</v>
       </c>
       <c r="H13" t="n">
-        <v>6000</v>
+        <v>5018.809239460667</v>
       </c>
       <c r="I13" t="n">
-        <v>26.79999999999995</v>
+        <v>19.79465054037149</v>
       </c>
       <c r="J13" t="n">
-        <v>655.9</v>
+        <v>523.6</v>
       </c>
       <c r="K13" t="n">
-        <v>0.09999999999999432</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -910,34 +910,34 @@
         <v>108</v>
       </c>
       <c r="B14" t="n">
-        <v>75.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>5158.979348109144</v>
+        <v>5169.362319120141</v>
       </c>
       <c r="F14" t="n">
-        <v>-411.6045852511102</v>
+        <v>-443.560084198627</v>
       </c>
       <c r="G14" t="n">
         <v>700</v>
       </c>
       <c r="H14" t="n">
-        <v>5018.809239460667</v>
+        <v>5013.617753955168</v>
       </c>
       <c r="I14" t="n">
-        <v>19.79465054037149</v>
+        <v>35.77240001413043</v>
       </c>
       <c r="J14" t="n">
         <v>523.6</v>
       </c>
       <c r="K14" t="n">
-        <v>1.800000000000004</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -945,69 +945,69 @@
         <v>108</v>
       </c>
       <c r="B15" t="n">
-        <v>84</v>
+        <v>95.2</v>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>5169.362319120141</v>
+        <v>5176.284299794141</v>
       </c>
       <c r="F15" t="n">
-        <v>-443.560084198627</v>
+        <v>-464.8637501636385</v>
       </c>
       <c r="G15" t="n">
         <v>700</v>
       </c>
       <c r="H15" t="n">
-        <v>5013.617753955168</v>
+        <v>4999.77379260717</v>
       </c>
       <c r="I15" t="n">
-        <v>35.77240001413043</v>
+        <v>78.37973194415326</v>
       </c>
       <c r="J15" t="n">
         <v>523.6</v>
       </c>
       <c r="K15" t="n">
-        <v>1.700000000000003</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="B16" t="n">
-        <v>95.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>5176.284299794141</v>
+        <v>4156.705448810804</v>
       </c>
       <c r="F16" t="n">
-        <v>-464.8637501636385</v>
+        <v>-462.9227056401646</v>
       </c>
       <c r="G16" t="n">
         <v>700</v>
       </c>
       <c r="H16" t="n">
-        <v>4999.77379260717</v>
+        <v>3788.046538572965</v>
       </c>
       <c r="I16" t="n">
-        <v>78.37973194415326</v>
+        <v>44.49275323180245</v>
       </c>
       <c r="J16" t="n">
-        <v>523.6</v>
+        <v>386.4</v>
       </c>
       <c r="K16" t="n">
-        <v>2.299999999999997</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1015,104 +1015,104 @@
         <v>126</v>
       </c>
       <c r="B17" t="n">
-        <v>78.40000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>4156.705448810804</v>
+        <v>4163.288643636481</v>
       </c>
       <c r="F17" t="n">
-        <v>-462.9227056401646</v>
+        <v>-471.9836959771646</v>
       </c>
       <c r="G17" t="n">
         <v>700</v>
       </c>
       <c r="H17" t="n">
-        <v>3788.046538572965</v>
+        <v>3755.130564444587</v>
       </c>
       <c r="I17" t="n">
-        <v>44.49275323180245</v>
+        <v>89.79770491679881</v>
       </c>
       <c r="J17" t="n">
         <v>386.4</v>
       </c>
       <c r="K17" t="n">
-        <v>1.600000000000001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B18" t="n">
-        <v>86.8</v>
+        <v>134.4</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>4163.288643636481</v>
+        <v>3719.156366604673</v>
       </c>
       <c r="F18" t="n">
-        <v>-471.9836959771646</v>
+        <v>-719.1563666046723</v>
       </c>
       <c r="G18" t="n">
         <v>700</v>
       </c>
       <c r="H18" t="n">
-        <v>3755.130564444587</v>
+        <v>2863.840004081426</v>
       </c>
       <c r="I18" t="n">
-        <v>89.79770491679881</v>
+        <v>136.1599959185756</v>
       </c>
       <c r="J18" t="n">
-        <v>386.4</v>
+        <v>303.1</v>
       </c>
       <c r="K18" t="n">
-        <v>1.400000000000006</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B19" t="n">
-        <v>134.4</v>
+        <v>103.6</v>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>3719.156366604673</v>
+        <v>2647.433575310219</v>
       </c>
       <c r="F19" t="n">
-        <v>-719.1563666046723</v>
+        <v>-564.2179144999909</v>
       </c>
       <c r="G19" t="n">
         <v>700</v>
       </c>
       <c r="H19" t="n">
-        <v>2863.840004081426</v>
+        <v>1809.291969137773</v>
       </c>
       <c r="I19" t="n">
-        <v>136.1599959185756</v>
+        <v>44.72760687501136</v>
       </c>
       <c r="J19" t="n">
-        <v>303.1</v>
+        <v>209.9999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>2.400000000000006</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1120,34 +1120,34 @@
         <v>144</v>
       </c>
       <c r="B20" t="n">
-        <v>103.6</v>
+        <v>114.8</v>
       </c>
       <c r="C20" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>2647.433575310219</v>
+        <v>2656.494565647218</v>
       </c>
       <c r="F20" t="n">
-        <v>-564.2179144999909</v>
+        <v>-570.8011093256664</v>
       </c>
       <c r="G20" t="n">
         <v>700</v>
       </c>
       <c r="H20" t="n">
-        <v>1809.291969137773</v>
+        <v>1727.743056104778</v>
       </c>
       <c r="I20" t="n">
-        <v>44.72760687501136</v>
+        <v>103.9763603060929</v>
       </c>
       <c r="J20" t="n">
         <v>209.9999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7999999999999972</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1155,69 +1155,34 @@
         <v>144</v>
       </c>
       <c r="B21" t="n">
-        <v>114.8</v>
+        <v>126</v>
       </c>
       <c r="C21" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>2656.494565647218</v>
+        <v>2738.043478680213</v>
       </c>
       <c r="F21" t="n">
-        <v>-570.8011093256664</v>
+        <v>-630.0498627567476</v>
       </c>
       <c r="G21" t="n">
         <v>700</v>
       </c>
       <c r="H21" t="n">
-        <v>1727.743056104778</v>
+        <v>1718.682065767779</v>
       </c>
       <c r="I21" t="n">
-        <v>103.9763603060929</v>
+        <v>110.5595551317688</v>
       </c>
       <c r="J21" t="n">
         <v>209.9999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6999999999999957</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>144</v>
-      </c>
-      <c r="B22" t="n">
-        <v>126</v>
-      </c>
-      <c r="C22" t="n">
-        <v>32</v>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2738.043478680213</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-630.0498627567476</v>
-      </c>
-      <c r="G22" t="n">
-        <v>700</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1718.682065767779</v>
-      </c>
-      <c r="I22" t="n">
-        <v>110.5595551317688</v>
-      </c>
-      <c r="J22" t="n">
-        <v>209.9999999999999</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1.199999999999996</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/5/search/FY3_Missile1_results/solutions_direction_153.0.xlsx
+++ b/5/search/FY3_Missile1_results/solutions_direction_153.0.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,177 +487,177 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72</v>
+        <v>76.5</v>
       </c>
       <c r="B2" t="n">
-        <v>100.8</v>
+        <v>108</v>
       </c>
       <c r="C2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>6996.76521705583</v>
+        <v>6705.938780300258</v>
       </c>
       <c r="F2" t="n">
-        <v>67.72789896164704</v>
+        <v>-59.55336071742613</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>6996.76521705583</v>
+        <v>6731.150879596696</v>
       </c>
       <c r="I2" t="n">
-        <v>67.72789896164704</v>
+        <v>45.46259068552294</v>
       </c>
       <c r="J2" t="n">
-        <v>700</v>
+        <v>695.1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81</v>
+        <v>76.5</v>
       </c>
       <c r="B3" t="n">
-        <v>78.40000000000001</v>
+        <v>112</v>
       </c>
       <c r="C3" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6732.084661052119</v>
+      </c>
+      <c r="F3" t="n">
+        <v>49.35207036711381</v>
+      </c>
+      <c r="G3" t="n">
+        <v>700</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6732.084661052119</v>
+      </c>
+      <c r="I3" t="n">
+        <v>49.35207036711381</v>
+      </c>
+      <c r="J3" t="n">
+        <v>700</v>
+      </c>
+      <c r="K3" t="n">
         <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>6441.520634129548</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-212.3484275042829</v>
-      </c>
-      <c r="G3" t="n">
-        <v>700</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6478.314020307011</v>
-      </c>
-      <c r="I3" t="n">
-        <v>19.95587020369356</v>
-      </c>
-      <c r="J3" t="n">
-        <v>655.9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81</v>
+        <v>76.5</v>
       </c>
       <c r="B4" t="n">
-        <v>89.59999999999999</v>
+        <v>122</v>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>6448.52889816335</v>
+        <v>6683.528025370091</v>
       </c>
       <c r="F4" t="n">
-        <v>-168.0999898456212</v>
+        <v>-152.9008730756032</v>
       </c>
       <c r="G4" t="n">
         <v>700</v>
       </c>
       <c r="H4" t="n">
-        <v>6476.56195429856</v>
+        <v>6740.488694150932</v>
       </c>
       <c r="I4" t="n">
-        <v>8.89376078902751</v>
+        <v>84.35738750142991</v>
       </c>
       <c r="J4" t="n">
         <v>680.4</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81</v>
+        <v>76.5</v>
       </c>
       <c r="B5" t="n">
-        <v>109.2</v>
+        <v>126</v>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>6478.31402030701</v>
+        <v>6705.938780300258</v>
       </c>
       <c r="F5" t="n">
-        <v>19.95587020369294</v>
+        <v>-59.55336071742613</v>
       </c>
       <c r="G5" t="n">
         <v>700</v>
       </c>
       <c r="H5" t="n">
-        <v>6478.31402030701</v>
+        <v>6735.352896146102</v>
       </c>
       <c r="I5" t="n">
-        <v>19.95587020369294</v>
+        <v>62.96524925268112</v>
       </c>
       <c r="J5" t="n">
-        <v>700</v>
+        <v>695.1</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>81</v>
+        <v>76.5</v>
       </c>
       <c r="B6" t="n">
-        <v>123.2</v>
+        <v>132</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>6462.545426230955</v>
+        <v>6739.554912695508</v>
       </c>
       <c r="F6" t="n">
-        <v>-79.60311452829683</v>
+        <v>80.46790781983918</v>
       </c>
       <c r="G6" t="n">
         <v>700</v>
       </c>
       <c r="H6" t="n">
-        <v>6481.818152323912</v>
+        <v>6739.554912695508</v>
       </c>
       <c r="I6" t="n">
-        <v>42.08008903302414</v>
+        <v>80.46790781983918</v>
       </c>
       <c r="J6" t="n">
-        <v>695.1</v>
+        <v>700</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -665,66 +665,66 @@
         <v>81</v>
       </c>
       <c r="B7" t="n">
-        <v>128.8</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>6483.570218332362</v>
+        <v>6446.776832154899</v>
       </c>
       <c r="F7" t="n">
-        <v>53.14219844769013</v>
+        <v>-179.1620992602866</v>
       </c>
       <c r="G7" t="n">
         <v>700</v>
       </c>
       <c r="H7" t="n">
-        <v>6483.570218332362</v>
+        <v>6478.689463023106</v>
       </c>
       <c r="I7" t="n">
-        <v>53.14219844769013</v>
+        <v>22.3263222211215</v>
       </c>
       <c r="J7" t="n">
-        <v>700</v>
+        <v>680.4</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B8" t="n">
-        <v>75.59999999999999</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>6000</v>
+        <v>6435.513550672003</v>
       </c>
       <c r="F8" t="n">
-        <v>-278.4000000000001</v>
+        <v>-250.2756597831367</v>
       </c>
       <c r="G8" t="n">
         <v>700</v>
       </c>
       <c r="H8" t="n">
-        <v>6000</v>
+        <v>6489.952744506003</v>
       </c>
       <c r="I8" t="n">
-        <v>23.99999999999989</v>
+        <v>93.43988274397122</v>
       </c>
       <c r="J8" t="n">
-        <v>621.6</v>
+        <v>655.9</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
@@ -732,34 +732,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6000</v>
+        <v>6480.566676603589</v>
       </c>
       <c r="F9" t="n">
-        <v>-312</v>
+        <v>34.17858230826323</v>
       </c>
       <c r="G9" t="n">
         <v>700</v>
       </c>
       <c r="H9" t="n">
-        <v>6000</v>
+        <v>6480.566676603589</v>
       </c>
       <c r="I9" t="n">
-        <v>24</v>
+        <v>34.17858230826323</v>
       </c>
       <c r="J9" t="n">
-        <v>621.6</v>
+        <v>700</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
@@ -767,34 +767,34 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>90</v>
+        <v>85.5</v>
       </c>
       <c r="B10" t="n">
-        <v>95.2</v>
+        <v>114</v>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>6000</v>
+        <v>6214.664085911384</v>
       </c>
       <c r="F10" t="n">
-        <v>-334.4000000000001</v>
+        <v>-272.4341749061618</v>
       </c>
       <c r="G10" t="n">
         <v>700</v>
       </c>
       <c r="H10" t="n">
-        <v>6000</v>
+        <v>6241.497096650307</v>
       </c>
       <c r="I10" t="n">
-        <v>46.39999999999992</v>
+        <v>68.51155323056793</v>
       </c>
       <c r="J10" t="n">
-        <v>621.6</v>
+        <v>655.9</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -802,139 +802,139 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>90</v>
+        <v>85.5</v>
       </c>
       <c r="B11" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>6000</v>
+        <v>6218.430122506321</v>
       </c>
       <c r="F11" t="n">
-        <v>-312</v>
+        <v>-224.5821428869717</v>
       </c>
       <c r="G11" t="n">
         <v>700</v>
       </c>
       <c r="H11" t="n">
-        <v>6000</v>
+        <v>6236.632632715181</v>
       </c>
       <c r="I11" t="n">
-        <v>24</v>
+        <v>6.702678539113975</v>
       </c>
       <c r="J11" t="n">
-        <v>655.9</v>
+        <v>680.4</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>90</v>
+        <v>85.5</v>
       </c>
       <c r="B12" t="n">
-        <v>128.8</v>
+        <v>134</v>
       </c>
       <c r="C12" t="n">
         <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>6000</v>
+        <v>6210.270376550625</v>
       </c>
       <c r="F12" t="n">
-        <v>-424</v>
+        <v>-328.2615455952168</v>
       </c>
       <c r="G12" t="n">
         <v>700</v>
       </c>
       <c r="H12" t="n">
-        <v>6000</v>
+        <v>6241.810933033218</v>
       </c>
       <c r="I12" t="n">
-        <v>91.20000000000005</v>
+        <v>72.49922256550065</v>
       </c>
       <c r="J12" t="n">
-        <v>621.6</v>
+        <v>655.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="B13" t="n">
-        <v>75.59999999999999</v>
+        <v>110</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>5158.979348109144</v>
+        <v>6000</v>
       </c>
       <c r="F13" t="n">
-        <v>-411.6045852511102</v>
+        <v>-360</v>
       </c>
       <c r="G13" t="n">
         <v>700</v>
       </c>
       <c r="H13" t="n">
-        <v>5018.809239460667</v>
+        <v>6000</v>
       </c>
       <c r="I13" t="n">
-        <v>19.79465054037149</v>
+        <v>80</v>
       </c>
       <c r="J13" t="n">
-        <v>523.6</v>
+        <v>621.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="B14" t="n">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>5169.362319120141</v>
+        <v>6000</v>
       </c>
       <c r="F14" t="n">
-        <v>-443.560084198627</v>
+        <v>-312</v>
       </c>
       <c r="G14" t="n">
         <v>700</v>
       </c>
       <c r="H14" t="n">
-        <v>5013.617753955168</v>
+        <v>6000</v>
       </c>
       <c r="I14" t="n">
-        <v>35.77240001413043</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>523.6</v>
+        <v>655.9</v>
       </c>
       <c r="K14" t="n">
         <v>2</v>
@@ -942,104 +942,104 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="B15" t="n">
-        <v>95.2</v>
+        <v>132</v>
       </c>
       <c r="C15" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>5176.284299794141</v>
+        <v>6000</v>
       </c>
       <c r="F15" t="n">
-        <v>-464.8637501636385</v>
+        <v>-360</v>
       </c>
       <c r="G15" t="n">
         <v>700</v>
       </c>
       <c r="H15" t="n">
-        <v>4999.77379260717</v>
+        <v>6000</v>
       </c>
       <c r="I15" t="n">
-        <v>78.37973194415326</v>
+        <v>36</v>
       </c>
       <c r="J15" t="n">
-        <v>523.6</v>
+        <v>655.9</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126</v>
+        <v>94.5</v>
       </c>
       <c r="B16" t="n">
-        <v>78.40000000000001</v>
+        <v>128</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>4156.705448810804</v>
+        <v>5799.144714936717</v>
       </c>
       <c r="F16" t="n">
-        <v>-462.9227056401646</v>
+        <v>-447.8916256431926</v>
       </c>
       <c r="G16" t="n">
         <v>700</v>
       </c>
       <c r="H16" t="n">
-        <v>3788.046538572965</v>
+        <v>5758.97365792406</v>
       </c>
       <c r="I16" t="n">
-        <v>44.49275323180245</v>
+        <v>62.53004922816893</v>
       </c>
       <c r="J16" t="n">
-        <v>386.4</v>
+        <v>621.6</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126</v>
+        <v>103.5</v>
       </c>
       <c r="B17" t="n">
-        <v>86.8</v>
+        <v>108</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>4163.288643636481</v>
+        <v>5394.909616885493</v>
       </c>
       <c r="F17" t="n">
-        <v>-471.9836959771646</v>
+        <v>-479.6171663292221</v>
       </c>
       <c r="G17" t="n">
         <v>700</v>
       </c>
       <c r="H17" t="n">
-        <v>3755.130564444587</v>
+        <v>5268.849120403304</v>
       </c>
       <c r="I17" t="n">
-        <v>89.79770491679881</v>
+        <v>45.46259068552331</v>
       </c>
       <c r="J17" t="n">
-        <v>386.4</v>
+        <v>577.5</v>
       </c>
       <c r="K17" t="n">
         <v>2</v>
@@ -1047,69 +1047,69 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135</v>
+        <v>103.5</v>
       </c>
       <c r="B18" t="n">
-        <v>134.4</v>
+        <v>126</v>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>3719.156366604673</v>
+        <v>5411.717683083119</v>
       </c>
       <c r="F18" t="n">
-        <v>-719.1563666046723</v>
+        <v>-549.6278005978547</v>
       </c>
       <c r="G18" t="n">
         <v>700</v>
       </c>
       <c r="H18" t="n">
-        <v>2863.840004081426</v>
+        <v>5264.647103853898</v>
       </c>
       <c r="I18" t="n">
-        <v>136.1599959185756</v>
+        <v>62.96524925268159</v>
       </c>
       <c r="J18" t="n">
-        <v>303.1</v>
+        <v>577.5</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="B19" t="n">
-        <v>103.6</v>
+        <v>108</v>
       </c>
       <c r="C19" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>2647.433575310219</v>
+        <v>5199.027950580136</v>
       </c>
       <c r="F19" t="n">
-        <v>-564.2179144999909</v>
+        <v>-534.8615097629618</v>
       </c>
       <c r="G19" t="n">
         <v>700</v>
       </c>
       <c r="H19" t="n">
-        <v>1809.291969137773</v>
+        <v>4998.784938225171</v>
       </c>
       <c r="I19" t="n">
-        <v>44.72760687501136</v>
+        <v>81.4231127962978</v>
       </c>
       <c r="J19" t="n">
-        <v>209.9999999999999</v>
+        <v>523.6</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1117,71 +1117,421 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>144</v>
+        <v>112.5</v>
       </c>
       <c r="B20" t="n">
-        <v>114.8</v>
+        <v>110</v>
       </c>
       <c r="C20" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>2656.494565647218</v>
+        <v>4989.715738556163</v>
       </c>
       <c r="F20" t="n">
-        <v>-570.8011093256664</v>
+        <v>-560.9580341702031</v>
       </c>
       <c r="G20" t="n">
         <v>700</v>
       </c>
       <c r="H20" t="n">
-        <v>1727.743056104778</v>
+        <v>4737.144673195204</v>
       </c>
       <c r="I20" t="n">
-        <v>103.9763603060929</v>
+        <v>48.80245728724617</v>
       </c>
       <c r="J20" t="n">
-        <v>209.9999999999999</v>
+        <v>523.6</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="B21" t="n">
+        <v>128</v>
+      </c>
+      <c r="C21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5020.330413145371</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-634.8683967711058</v>
+      </c>
+      <c r="G21" t="n">
+        <v>700</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4726.429537088981</v>
+      </c>
+      <c r="I21" t="n">
+        <v>74.67108419756232</v>
+      </c>
+      <c r="J21" t="n">
+        <v>523.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>102</v>
+      </c>
+      <c r="C22" t="n">
+        <v>28</v>
+      </c>
+      <c r="D22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4507.74409917125</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-564.8596906047123</v>
+      </c>
+      <c r="G22" t="n">
+        <v>700</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4134.680123964063</v>
+      </c>
+      <c r="I22" t="n">
+        <v>43.92538674410957</v>
+      </c>
+      <c r="J22" t="n">
+        <v>459.9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="B23" t="n">
+        <v>116</v>
+      </c>
+      <c r="C23" t="n">
+        <v>24</v>
+      </c>
+      <c r="D23" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4545.363995830799</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-626.2497824382071</v>
+      </c>
+      <c r="G23" t="n">
+        <v>700</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4121.095161281448</v>
+      </c>
+      <c r="I23" t="n">
+        <v>66.09403101731584</v>
+      </c>
+      <c r="J23" t="n">
+        <v>459.9</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>134</v>
+      </c>
+      <c r="C24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4599.703846561257</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-714.9243595310327</v>
+      </c>
+      <c r="G24" t="n">
+        <v>700</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4109.600192857697</v>
+      </c>
+      <c r="I24" t="n">
+        <v>84.85211463310588</v>
+      </c>
+      <c r="J24" t="n">
+        <v>459.9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="B25" t="n">
+        <v>100</v>
+      </c>
+      <c r="C25" t="n">
+        <v>32</v>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3921.766245343413</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-566.7009100799005</v>
+      </c>
+      <c r="G25" t="n">
+        <v>700</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3402.207806679266</v>
+      </c>
+      <c r="I25" t="n">
+        <v>41.62386240012438</v>
+      </c>
+      <c r="J25" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>112</v>
+      </c>
+      <c r="C26" t="n">
+        <v>28</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3963.330920436545</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-615.3668918783023</v>
+      </c>
+      <c r="G26" t="n">
+        <v>700</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3381.4254691327</v>
+      </c>
+      <c r="I26" t="n">
+        <v>65.95685329932553</v>
+      </c>
+      <c r="J26" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="B27" t="n">
+        <v>114</v>
+      </c>
+      <c r="C27" t="n">
+        <v>32</v>
+      </c>
+      <c r="D27" t="n">
+        <v>9</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3226.039037491087</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-630.8135196914895</v>
+      </c>
+      <c r="G27" t="n">
+        <v>700</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2445.862516785455</v>
+      </c>
+      <c r="I27" t="n">
+        <v>35.52017789527906</v>
+      </c>
+      <c r="J27" t="n">
+        <v>303.1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
         <v>144</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B28" t="n">
+        <v>104</v>
+      </c>
+      <c r="C28" t="n">
+        <v>40</v>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2634.489303400219</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-554.8133504633115</v>
+      </c>
+      <c r="G28" t="n">
+        <v>700</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1793.111629250274</v>
+      </c>
+      <c r="I28" t="n">
+        <v>56.48331192086061</v>
+      </c>
+      <c r="J28" t="n">
+        <v>209.9999999999999</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>144</v>
+      </c>
+      <c r="B29" t="n">
+        <v>114</v>
+      </c>
+      <c r="C29" t="n">
+        <v>36</v>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2679.794255085216</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-587.7293245916894</v>
+      </c>
+      <c r="G29" t="n">
+        <v>700</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1757.514881497776</v>
+      </c>
+      <c r="I29" t="n">
+        <v>82.34586302173011</v>
+      </c>
+      <c r="J29" t="n">
+        <v>209.9999999999999</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>144</v>
+      </c>
+      <c r="B30" t="n">
         <v>126</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C30" t="n">
         <v>32</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D30" t="n">
         <v>10</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E30" t="n">
         <v>2738.043478680213</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F30" t="n">
         <v>-630.0498627567476</v>
       </c>
-      <c r="G21" t="n">
-        <v>700</v>
-      </c>
-      <c r="H21" t="n">
+      <c r="G30" t="n">
+        <v>700</v>
+      </c>
+      <c r="H30" t="n">
         <v>1718.682065767779</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I30" t="n">
         <v>110.5595551317688</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J30" t="n">
         <v>209.9999999999999</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="B31" t="n">
+        <v>118</v>
+      </c>
+      <c r="C31" t="n">
+        <v>40</v>
+      </c>
+      <c r="D31" t="n">
+        <v>11</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1975.538424248685</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-533.8067745407211</v>
+      </c>
+      <c r="G31" t="n">
+        <v>700</v>
+      </c>
+      <c r="H31" t="n">
+        <v>868.8114909170731</v>
+      </c>
+      <c r="I31" t="n">
+        <v>144.3963624605806</v>
+      </c>
+      <c r="J31" t="n">
+        <v>107.0999999999999</v>
+      </c>
+      <c r="K31" t="n">
         <v>1</v>
       </c>
     </row>
